--- a/forward/Clase 10 Forward/carry_usd_clp.xlsx
+++ b/forward/Clase 10 Forward/carry_usd_clp.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\Desarrollo\MEF\Catedras\Economía Financiera\economia-financiera\forward\Clase 10 Forward\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C568B4-A080-450F-9AF0-D958D3591585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE732E3-8EE2-4A4E-9F24-504A2783E592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{572737A0-2389-4671-988A-502B8AA1025B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{572737A0-2389-4671-988A-502B8AA1025B}"/>
   </bookViews>
   <sheets>
     <sheet name="Arbitraje" sheetId="3" r:id="rId1"/>
-    <sheet name="Replicación" sheetId="4" r:id="rId2"/>
-    <sheet name="Ejemplo Replicación" sheetId="5" r:id="rId3"/>
-    <sheet name="Carry Trade" sheetId="1" r:id="rId4"/>
+    <sheet name="Venta Corta" sheetId="6" r:id="rId2"/>
+    <sheet name="Replicación" sheetId="4" r:id="rId3"/>
+    <sheet name="Ejemplo Replicación" sheetId="5" r:id="rId4"/>
+    <sheet name="Carry Trade" sheetId="1" r:id="rId5"/>
+    <sheet name="Hoja2" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="116">
   <si>
     <t>S_0</t>
   </si>
@@ -292,20 +294,119 @@
   <si>
     <t>=</t>
   </si>
+  <si>
+    <t>Vender lo que no tengo</t>
+  </si>
+  <si>
+    <t>Vendo el activo que no tengo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pido prestado </t>
+  </si>
+  <si>
+    <t>con el compromiso de devolverlo</t>
+  </si>
+  <si>
+    <t>A + costo de carry</t>
+  </si>
+  <si>
+    <t>A = 105</t>
+  </si>
+  <si>
+    <t>vuelvo a comprar a 50</t>
+  </si>
+  <si>
+    <t>precio sube a las nubes</t>
+  </si>
+  <si>
+    <t>lo vendi a 100 y tengo que devolverlo a 200 (compro a 200)</t>
+  </si>
+  <si>
+    <t>USD /CLP</t>
+  </si>
+  <si>
+    <t>ptos fwd</t>
+  </si>
+  <si>
+    <t>Futuros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margen </t>
+  </si>
+  <si>
+    <t>Mmantencion</t>
+  </si>
+  <si>
+    <t>futuro</t>
+  </si>
+  <si>
+    <t>spot</t>
+  </si>
+  <si>
+    <t>1 año</t>
+  </si>
+  <si>
+    <t>COMPRA</t>
+  </si>
+  <si>
+    <t>VENTA</t>
+  </si>
+  <si>
+    <t>precio spot</t>
+  </si>
+  <si>
+    <t>t=1</t>
+  </si>
+  <si>
+    <t>magin call</t>
+  </si>
+  <si>
+    <t>final del día</t>
+  </si>
+  <si>
+    <t>margen comprador</t>
+  </si>
+  <si>
+    <t>margen vendedor</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>activos del comprador</t>
+  </si>
+  <si>
+    <t>Margen inicial</t>
+  </si>
+  <si>
+    <t>Nominal</t>
+  </si>
+  <si>
+    <t>cuentas</t>
+  </si>
+  <si>
+    <t>porque baje del margen account 4%*1000 * 1 =  40</t>
+  </si>
+  <si>
+    <t>1 unidad contrato</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="9">
     <numFmt numFmtId="42" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="172" formatCode="0.0000"/>
-    <numFmt numFmtId="173" formatCode="0.000"/>
-    <numFmt numFmtId="174" formatCode="0.0%"/>
-    <numFmt numFmtId="175" formatCode="0.000%"/>
-    <numFmt numFmtId="177" formatCode="_ &quot;$&quot;* #,##0.00_ ;_ &quot;$&quot;* \-#,##0.00_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.000%"/>
+    <numFmt numFmtId="168" formatCode="_ &quot;$&quot;* #,##0.00_ ;_ &quot;$&quot;* \-#,##0.00_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="170" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,6 +447,14 @@
       <b/>
       <sz val="20"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -407,7 +516,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -784,13 +893,104 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -811,11 +1011,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -825,45 +1021,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="172" fontId="0" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -879,7 +1064,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -907,14 +1092,49 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="2" fillId="5" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="2" fillId="5" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="8" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="39" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Millares [0]" xfId="3" builtinId="6"/>
     <cellStyle name="Moneda [0]" xfId="1" builtinId="7"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
@@ -2292,8 +2512,8 @@
       <xdr:rowOff>15875</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="187294" cy="180755"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="CuadroTexto 3">
@@ -2335,6 +2555,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2382,7 +2603,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="CuadroTexto 3">
@@ -2446,8 +2667,8 @@
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="186654" cy="179921"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="CuadroTexto 4">
@@ -2489,6 +2710,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2536,7 +2758,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="CuadroTexto 4">
@@ -2600,8 +2822,8 @@
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="187295" cy="180819"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="CuadroTexto 5">
@@ -2643,6 +2865,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2690,7 +2913,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="CuadroTexto 5">
@@ -2754,8 +2977,8 @@
       <xdr:rowOff>3175</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="186653" cy="179986"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="CuadroTexto 6">
@@ -2797,6 +3020,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2844,7 +3068,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="CuadroTexto 6">
@@ -3430,7 +3654,7 @@
               </a:r>
               <a:r>
                 <a:rPr lang="es-CL" sz="1100" b="1" baseline="0"/>
-                <a:t>beneficio total de la estrategia es 0,15 </a:t>
+                <a:t>beneficio total de la estrategia es 0,15 - 0,2 = 0,13 </a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="es-CL" sz="1100" baseline="0"/>
@@ -3584,7 +3808,7 @@
               </a:r>
               <a:r>
                 <a:rPr lang="es-CL" sz="1100" b="1" baseline="0"/>
-                <a:t>beneficio total de la estrategia es 0,15 </a:t>
+                <a:t>beneficio total de la estrategia es 0,15 - 0,2 = 0,13 </a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="es-CL" sz="1100" baseline="0"/>
@@ -3738,10 +3962,134 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>130175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>53975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="CuadroTexto 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D533846-0023-B7FA-3216-1FCFA0992AC5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10458450" y="3987800"/>
+          <a:ext cx="2590800" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-CL" sz="1100"/>
+            <a:t>***Por ejemplo el bono A fue sobre vendido por una contraparte debido</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-CL" sz="1100" baseline="0"/>
+            <a:t> a shocks de liquidez.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-CL" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>20223</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>153078</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A6F7AAD-398E-015C-80D9-C52C848BF480}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8402223" cy="4858428"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3844,8 +4192,8 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="CuadroTexto 6">
@@ -3911,6 +4259,7 @@
               </a:endParaRPr>
             </a:p>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -3954,7 +4303,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -3966,7 +4315,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -3985,6 +4334,7 @@
               </a:endParaRPr>
             </a:p>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -4081,7 +4431,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -4093,7 +4443,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -4217,6 +4567,7 @@
               </a:r>
             </a:p>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -4368,7 +4719,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="CuadroTexto 6">
@@ -4780,8 +5131,8 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="CuadroTexto 9">
@@ -4830,6 +5181,7 @@
             <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -4844,7 +5196,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -4857,7 +5209,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -4871,7 +5223,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -4885,7 +5237,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -4899,7 +5251,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -4914,7 +5266,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -4927,7 +5279,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -4939,7 +5291,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -4955,7 +5307,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -5062,7 +5414,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="CuadroTexto 9">
@@ -5236,8 +5588,8 @@
       <xdr:row>40</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="CuadroTexto 15">
@@ -5303,6 +5655,7 @@
               </a:endParaRPr>
             </a:p>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -5346,7 +5699,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -5358,7 +5711,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -5377,6 +5730,7 @@
               </a:endParaRPr>
             </a:p>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -5473,7 +5827,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -5485,7 +5839,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -5538,6 +5892,7 @@
               </a:r>
             </a:p>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -5716,7 +6071,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="CuadroTexto 15">
@@ -6106,8 +6461,8 @@
       <xdr:row>49</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="CuadroTexto 18">
@@ -6156,6 +6511,7 @@
             <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -6170,7 +6526,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6183,7 +6539,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6197,7 +6553,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6211,7 +6567,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -6225,7 +6581,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6240,7 +6596,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -6253,7 +6609,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -6265,7 +6621,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -6281,7 +6637,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6388,7 +6744,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="CuadroTexto 18">
@@ -6482,8 +6838,8 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>126724</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="21" name="CuadroTexto 20">
@@ -6532,6 +6888,7 @@
             <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -6546,7 +6903,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6559,7 +6916,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6573,7 +6930,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6587,7 +6944,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -6601,7 +6958,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6616,7 +6973,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -6629,7 +6986,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -6641,7 +6998,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -6657,7 +7014,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6764,7 +7121,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="21" name="CuadroTexto 20">
@@ -6858,8 +7215,8 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>188015</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="22" name="CuadroTexto 21">
@@ -6908,6 +7265,7 @@
             <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -6922,7 +7280,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6935,7 +7293,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6949,7 +7307,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6978,7 +7336,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -7006,7 +7364,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -7019,7 +7377,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -7033,7 +7391,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -7047,7 +7405,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -7061,7 +7419,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -7076,7 +7434,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -7089,7 +7447,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -7101,7 +7459,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -7117,7 +7475,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -7133,7 +7491,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="22" name="CuadroTexto 21">
@@ -7258,8 +7616,8 @@
       <xdr:rowOff>176704</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="473848" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="23" name="CuadroTexto 22">
@@ -7301,6 +7659,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -7371,7 +7730,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="23" name="CuadroTexto 22">
@@ -7435,8 +7794,8 @@
       <xdr:rowOff>183055</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="680250" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="25" name="CuadroTexto 24">
@@ -7478,6 +7837,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -7565,7 +7925,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="25" name="CuadroTexto 24">
@@ -7629,8 +7989,8 @@
       <xdr:rowOff>160173</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="999824" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="26" name="CuadroTexto 25">
@@ -7672,6 +8032,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -7754,7 +8115,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="26" name="CuadroTexto 25">
@@ -7823,8 +8184,8 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>94974</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="27" name="CuadroTexto 26">
@@ -7873,6 +8234,7 @@
             <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -7887,7 +8249,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -7900,7 +8262,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -7914,7 +8276,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -7928,7 +8290,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -8076,7 +8438,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="27" name="CuadroTexto 26">
@@ -8167,8 +8529,8 @@
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>638624</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>180974</xdr:rowOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>3174</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -8204,7 +8566,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -8258,8 +8620,8 @@
       <xdr:rowOff>1587</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="160172" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="CuadroTexto 2">
@@ -8301,6 +8663,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -8340,7 +8703,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="CuadroTexto 2">
@@ -8404,8 +8767,8 @@
       <xdr:rowOff>173037</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="171907" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="CuadroTexto 3">
@@ -8447,6 +8810,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -8486,7 +8850,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="CuadroTexto 3">
@@ -8550,8 +8914,8 @@
       <xdr:rowOff>179387</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="171907" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="CuadroTexto 4">
@@ -8593,6 +8957,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -8632,7 +8997,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="CuadroTexto 4">
@@ -8701,8 +9066,8 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="CuadroTexto 5">
@@ -8751,6 +9116,7 @@
             <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -8765,7 +9131,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -8778,7 +9144,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -8792,7 +9158,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -8806,7 +9172,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -8820,7 +9186,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -8835,7 +9201,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -8848,7 +9214,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -8860,7 +9226,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -8876,7 +9242,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -8983,7 +9349,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="CuadroTexto 5">
@@ -9077,8 +9443,8 @@
       <xdr:row>38</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="CuadroTexto 6">
@@ -9162,6 +9528,7 @@
               </a:endParaRPr>
             </a:p>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -9314,7 +9681,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="CuadroTexto 6">
@@ -9432,7 +9799,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -9491,8 +9858,8 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>73025</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="CuadroTexto 6">
@@ -9541,6 +9908,7 @@
             <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -9555,7 +9923,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -9568,7 +9936,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -9582,7 +9950,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -9596,7 +9964,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -9610,7 +9978,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -9625,7 +9993,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -9638,7 +10006,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -9650,7 +10018,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -9666,7 +10034,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -9773,7 +10141,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="CuadroTexto 6">
@@ -9867,8 +10235,8 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>152399</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="CuadroTexto 7">
@@ -9917,6 +10285,7 @@
             <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -9931,7 +10300,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -9944,7 +10313,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -9958,7 +10327,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -9987,7 +10356,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -10015,7 +10384,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -10028,7 +10397,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -10042,7 +10411,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -10056,7 +10425,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -10085,7 +10454,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -10100,7 +10469,7 @@
                                       <a:schemeClr val="dk1"/>
                                     </a:solidFill>
                                     <a:effectLst/>
-                                    <a:latin typeface="+mn-lt"/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                     <a:ea typeface="+mn-ea"/>
                                     <a:cs typeface="+mn-cs"/>
                                   </a:rPr>
@@ -10113,7 +10482,7 @@
                                       <a:schemeClr val="dk1"/>
                                     </a:solidFill>
                                     <a:effectLst/>
-                                    <a:latin typeface="+mn-lt"/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                     <a:ea typeface="+mn-ea"/>
                                     <a:cs typeface="+mn-cs"/>
                                   </a:rPr>
@@ -10140,7 +10509,7 @@
                                           <a:schemeClr val="dk1"/>
                                         </a:solidFill>
                                         <a:effectLst/>
-                                        <a:latin typeface="+mn-lt"/>
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                         <a:ea typeface="+mn-ea"/>
                                         <a:cs typeface="+mn-cs"/>
                                       </a:rPr>
@@ -10172,7 +10541,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -10366,7 +10735,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="CuadroTexto 7">
@@ -10574,8 +10943,8 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>130176</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="CuadroTexto 8">
@@ -10624,6 +10993,7 @@
             <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -10638,7 +11008,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -10651,7 +11021,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -10665,7 +11035,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -10679,7 +11049,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -10708,7 +11078,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -10723,7 +11093,7 @@
                                       <a:schemeClr val="dk1"/>
                                     </a:solidFill>
                                     <a:effectLst/>
-                                    <a:latin typeface="+mn-lt"/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                     <a:ea typeface="+mn-ea"/>
                                     <a:cs typeface="+mn-cs"/>
                                   </a:rPr>
@@ -10736,7 +11106,7 @@
                                       <a:schemeClr val="dk1"/>
                                     </a:solidFill>
                                     <a:effectLst/>
-                                    <a:latin typeface="+mn-lt"/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                     <a:ea typeface="+mn-ea"/>
                                     <a:cs typeface="+mn-cs"/>
                                   </a:rPr>
@@ -10763,7 +11133,7 @@
                                           <a:schemeClr val="dk1"/>
                                         </a:solidFill>
                                         <a:effectLst/>
-                                        <a:latin typeface="+mn-lt"/>
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                         <a:ea typeface="+mn-ea"/>
                                         <a:cs typeface="+mn-cs"/>
                                       </a:rPr>
@@ -10795,7 +11165,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -10918,7 +11288,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="CuadroTexto 8">
@@ -11036,8 +11406,8 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="CuadroTexto 10">
@@ -11086,6 +11456,7 @@
             <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -11184,7 +11555,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="CuadroTexto 10">
@@ -11266,8 +11637,8 @@
       <xdr:row>39</xdr:row>
       <xdr:rowOff>66674</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="CuadroTexto 11">
@@ -11392,7 +11763,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="CuadroTexto 11">
@@ -11487,8 +11858,8 @@
       <xdr:row>26</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="CuadroTexto 12">
@@ -11537,6 +11908,7 @@
             <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -11551,7 +11923,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -11564,7 +11936,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -11578,7 +11950,7 @@
                               <a:schemeClr val="dk1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -11592,7 +11964,7 @@
                           <a:schemeClr val="dk1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -11621,7 +11993,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -11691,7 +12063,7 @@
                                   <a:schemeClr val="dk1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -11797,7 +12169,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="CuadroTexto 12">
@@ -12254,13 +12626,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" s="19" customFormat="1" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
     </row>
     <row r="10" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="11" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -12281,22 +12653,22 @@
       </c>
     </row>
     <row r="12" spans="2:10" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="23">
+      <c r="B12" s="21">
         <v>0</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="12"/>
     </row>
     <row r="13" spans="2:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="24">
+      <c r="B13" s="22">
         <v>0</v>
       </c>
       <c r="C13" s="14" t="s">
@@ -12311,7 +12683,7 @@
       <c r="F13" s="15"/>
     </row>
     <row r="14" spans="2:10" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="23" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="9" t="s">
@@ -12326,7 +12698,7 @@
       <c r="F14" s="10"/>
     </row>
     <row r="15" spans="2:10" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="22" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="14" t="s">
@@ -12350,6 +12722,79 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C07CA8CF-E9F7-4876-BC3D-22EF83E66933}">
+  <dimension ref="M5:Q20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="5" spans="13:17" x14ac:dyDescent="0.35">
+      <c r="M5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="13:17" x14ac:dyDescent="0.35">
+      <c r="M7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="13:17" x14ac:dyDescent="0.35">
+      <c r="M10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="13:17" x14ac:dyDescent="0.35">
+      <c r="Q11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="13:17" x14ac:dyDescent="0.35">
+      <c r="M12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="13:17" x14ac:dyDescent="0.35">
+      <c r="Q13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="13:17" x14ac:dyDescent="0.35">
+      <c r="M14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="13:17" x14ac:dyDescent="0.35">
+      <c r="M16" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="13:17" x14ac:dyDescent="0.35">
+      <c r="M18" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q18">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="13:17" x14ac:dyDescent="0.35">
+      <c r="M20" s="47">
+        <v>0.05</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA499CD-4EC9-447B-B7EF-12231C465AD7}">
   <dimension ref="F1:R41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -12367,12 +12812,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="6:18" s="19" customFormat="1" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="84" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
     </row>
     <row r="2" spans="6:18" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="6:18" x14ac:dyDescent="0.35">
@@ -12391,19 +12836,19 @@
         <f>+K3/12</f>
         <v>0.25</v>
       </c>
-      <c r="N4" s="36" t="s">
+      <c r="N4" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="O4" s="36" t="s">
+      <c r="O4" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="P4" s="36" t="s">
+      <c r="P4" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="Q4" s="36" t="s">
+      <c r="Q4" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="R4" s="37" t="s">
+      <c r="R4" s="32" t="s">
         <v>55</v>
       </c>
     </row>
@@ -12414,22 +12859,22 @@
       <c r="K5" s="12">
         <v>1783.28</v>
       </c>
-      <c r="N5" s="36">
+      <c r="N5" s="32">
         <v>1660</v>
       </c>
-      <c r="O5" s="36">
+      <c r="O5" s="32">
         <f>+N5-$K$5</f>
         <v>-123.27999999999997</v>
       </c>
-      <c r="P5" s="36">
+      <c r="P5" s="32">
         <f>+$K$6-N5</f>
         <v>132.13000000000011</v>
       </c>
-      <c r="Q5" s="36">
+      <c r="Q5" s="32">
         <f>+O5+P5</f>
         <v>8.8500000000001364</v>
       </c>
-      <c r="R5" s="36">
+      <c r="R5" s="32">
         <v>0</v>
       </c>
     </row>
@@ -12440,23 +12885,23 @@
       <c r="K6" s="12">
         <v>1792.13</v>
       </c>
-      <c r="M6" s="33"/>
-      <c r="N6" s="36">
+      <c r="M6" s="29"/>
+      <c r="N6" s="32">
         <v>1680</v>
       </c>
-      <c r="O6" s="36">
-        <f>+N6-$K$5</f>
+      <c r="O6" s="32">
+        <f t="shared" ref="O5:O16" si="0">+N6-$K$5</f>
         <v>-103.27999999999997</v>
       </c>
-      <c r="P6" s="36">
-        <f>+$K$6-N6</f>
+      <c r="P6" s="32">
+        <f t="shared" ref="P5:P16" si="1">+$K$6-N6</f>
         <v>112.13000000000011</v>
       </c>
-      <c r="Q6" s="36">
-        <f>+O6+P6</f>
+      <c r="Q6" s="32">
+        <f t="shared" ref="Q5:Q16" si="2">+O6+P6</f>
         <v>8.8500000000001364</v>
       </c>
-      <c r="R6" s="36">
+      <c r="R6" s="32">
         <v>0</v>
       </c>
     </row>
@@ -12464,47 +12909,47 @@
       <c r="J7" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="35">
+      <c r="K7" s="31">
         <v>0.02</v>
       </c>
-      <c r="N7" s="36">
+      <c r="N7" s="32">
         <v>1700</v>
       </c>
-      <c r="O7" s="36">
-        <f>+N7-$K$5</f>
+      <c r="O7" s="32">
+        <f t="shared" si="0"/>
         <v>-83.279999999999973</v>
       </c>
-      <c r="P7" s="36">
-        <f>+$K$6-N7</f>
+      <c r="P7" s="32">
+        <f t="shared" si="1"/>
         <v>92.130000000000109</v>
       </c>
-      <c r="Q7" s="36">
-        <f>+O7+P7</f>
+      <c r="Q7" s="32">
+        <f t="shared" si="2"/>
         <v>8.8500000000001364</v>
       </c>
-      <c r="R7" s="36">
+      <c r="R7" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="6:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="J8" s="11"/>
       <c r="K8" s="12"/>
-      <c r="N8" s="36">
+      <c r="N8" s="32">
         <v>1720</v>
       </c>
-      <c r="O8" s="36">
-        <f>+N8-$K$5</f>
+      <c r="O8" s="32">
+        <f t="shared" si="0"/>
         <v>-63.279999999999973</v>
       </c>
-      <c r="P8" s="36">
-        <f>+$K$6-N8</f>
+      <c r="P8" s="32">
+        <f t="shared" si="1"/>
         <v>72.130000000000109</v>
       </c>
-      <c r="Q8" s="36">
-        <f>+O8+P8</f>
+      <c r="Q8" s="32">
+        <f t="shared" si="2"/>
         <v>8.8500000000001364</v>
       </c>
-      <c r="R8" s="36">
+      <c r="R8" s="32">
         <v>0</v>
       </c>
     </row>
@@ -12516,22 +12961,22 @@
         <f>+K5*(1+K7)^K4</f>
         <v>1792.1302966158628</v>
       </c>
-      <c r="N9" s="36">
+      <c r="N9" s="32">
         <v>1740</v>
       </c>
-      <c r="O9" s="36">
-        <f>+N9-$K$5</f>
+      <c r="O9" s="32">
+        <f t="shared" si="0"/>
         <v>-43.279999999999973</v>
       </c>
-      <c r="P9" s="36">
-        <f>+$K$6-N9</f>
+      <c r="P9" s="32">
+        <f t="shared" si="1"/>
         <v>52.130000000000109</v>
       </c>
-      <c r="Q9" s="36">
-        <f>+O9+P9</f>
+      <c r="Q9" s="32">
+        <f t="shared" si="2"/>
         <v>8.8500000000001364</v>
       </c>
-      <c r="R9" s="36">
+      <c r="R9" s="32">
         <v>0</v>
       </c>
     </row>
@@ -12543,71 +12988,71 @@
         <f>+K9-K5</f>
         <v>8.8502966158628169</v>
       </c>
-      <c r="N10" s="36">
+      <c r="N10" s="32">
         <v>1760</v>
       </c>
-      <c r="O10" s="36">
-        <f>+N10-$K$5</f>
+      <c r="O10" s="32">
+        <f t="shared" si="0"/>
         <v>-23.279999999999973</v>
       </c>
-      <c r="P10" s="36">
-        <f>+$K$6-N10</f>
+      <c r="P10" s="32">
+        <f t="shared" si="1"/>
         <v>32.130000000000109</v>
       </c>
-      <c r="Q10" s="36">
-        <f>+O10+P10</f>
+      <c r="Q10" s="32">
+        <f t="shared" si="2"/>
         <v>8.8500000000001364</v>
       </c>
-      <c r="R10" s="36">
+      <c r="R10" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="6:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J11" s="28" t="s">
+      <c r="J11" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="K11" s="45">
+      <c r="K11" s="38">
         <f>+K6-K9</f>
         <v>-2.9661586268048268E-4</v>
       </c>
-      <c r="N11" s="36">
+      <c r="N11" s="32">
         <v>1780</v>
       </c>
-      <c r="O11" s="36">
-        <f>+N11-$K$5</f>
+      <c r="O11" s="32">
+        <f t="shared" si="0"/>
         <v>-3.2799999999999727</v>
       </c>
-      <c r="P11" s="36">
-        <f>+$K$6-N11</f>
+      <c r="P11" s="32">
+        <f t="shared" si="1"/>
         <v>12.130000000000109</v>
       </c>
-      <c r="Q11" s="36">
-        <f>+O11+P11</f>
+      <c r="Q11" s="32">
+        <f t="shared" si="2"/>
         <v>8.8500000000001364</v>
       </c>
-      <c r="R11" s="36">
+      <c r="R11" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="6:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="J12" s="13"/>
       <c r="K12" s="15"/>
-      <c r="N12" s="36">
+      <c r="N12" s="32">
         <v>1800</v>
       </c>
-      <c r="O12" s="36">
-        <f>+N12-$K$5</f>
+      <c r="O12" s="32">
+        <f t="shared" si="0"/>
         <v>16.720000000000027</v>
       </c>
-      <c r="P12" s="36">
-        <f>+$K$6-N12</f>
+      <c r="P12" s="32">
+        <f t="shared" si="1"/>
         <v>-7.8699999999998909</v>
       </c>
-      <c r="Q12" s="36">
-        <f>+O12+P12</f>
+      <c r="Q12" s="32">
+        <f t="shared" si="2"/>
         <v>8.8500000000001364</v>
       </c>
-      <c r="R12" s="36">
+      <c r="R12" s="32">
         <v>0</v>
       </c>
     </row>
@@ -12619,22 +13064,22 @@
         <f>+K6-K5</f>
         <v>8.8500000000001364</v>
       </c>
-      <c r="N13" s="36">
+      <c r="N13" s="32">
         <v>1820</v>
       </c>
-      <c r="O13" s="36">
-        <f>+N13-$K$5</f>
+      <c r="O13" s="32">
+        <f t="shared" si="0"/>
         <v>36.720000000000027</v>
       </c>
-      <c r="P13" s="36">
-        <f>+$K$6-N13</f>
+      <c r="P13" s="32">
+        <f t="shared" si="1"/>
         <v>-27.869999999999891</v>
       </c>
-      <c r="Q13" s="36">
-        <f>+O13+P13</f>
+      <c r="Q13" s="32">
+        <f t="shared" si="2"/>
         <v>8.8500000000001364</v>
       </c>
-      <c r="R13" s="36">
+      <c r="R13" s="32">
         <v>0</v>
       </c>
     </row>
@@ -12642,97 +13087,97 @@
       <c r="J14" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="K14" s="34">
+      <c r="K14" s="30">
         <f>+(K13/K5)*4</f>
         <v>1.9851060966309578E-2</v>
       </c>
-      <c r="N14" s="36">
+      <c r="N14" s="32">
         <v>1840</v>
       </c>
-      <c r="O14" s="36">
-        <f>+N14-$K$5</f>
+      <c r="O14" s="32">
+        <f t="shared" si="0"/>
         <v>56.720000000000027</v>
       </c>
-      <c r="P14" s="36">
-        <f>+$K$6-N14</f>
+      <c r="P14" s="32">
+        <f t="shared" si="1"/>
         <v>-47.869999999999891</v>
       </c>
-      <c r="Q14" s="36">
-        <f>+O14+P14</f>
+      <c r="Q14" s="32">
+        <f t="shared" si="2"/>
         <v>8.8500000000001364</v>
       </c>
-      <c r="R14" s="36">
+      <c r="R14" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="6:18" x14ac:dyDescent="0.35">
-      <c r="N15" s="36">
+      <c r="N15" s="32">
         <v>1860</v>
       </c>
-      <c r="O15" s="36">
-        <f>+N15-$K$5</f>
+      <c r="O15" s="32">
+        <f t="shared" si="0"/>
         <v>76.720000000000027</v>
       </c>
-      <c r="P15" s="36">
-        <f>+$K$6-N15</f>
+      <c r="P15" s="32">
+        <f t="shared" si="1"/>
         <v>-67.869999999999891</v>
       </c>
-      <c r="Q15" s="36">
-        <f>+O15+P15</f>
+      <c r="Q15" s="32">
+        <f t="shared" si="2"/>
         <v>8.8500000000001364</v>
       </c>
-      <c r="R15" s="36">
+      <c r="R15" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="6:18" x14ac:dyDescent="0.35">
-      <c r="N16" s="36">
+      <c r="N16" s="32">
         <v>1880</v>
       </c>
-      <c r="O16" s="36">
-        <f>+N16-$K$5</f>
+      <c r="O16" s="32">
+        <f t="shared" si="0"/>
         <v>96.720000000000027</v>
       </c>
-      <c r="P16" s="36">
-        <f>+$K$6-N16</f>
+      <c r="P16" s="32">
+        <f t="shared" si="1"/>
         <v>-87.869999999999891</v>
       </c>
-      <c r="Q16" s="36">
-        <f>+O16+P16</f>
+      <c r="Q16" s="32">
+        <f t="shared" si="2"/>
         <v>8.8500000000001364</v>
       </c>
-      <c r="R16" s="36">
+      <c r="R16" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="6:12" x14ac:dyDescent="0.35">
-      <c r="F26" s="39"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="39"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="39"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="34"/>
     </row>
     <row r="27" spans="6:12" x14ac:dyDescent="0.35">
-      <c r="F27" s="39"/>
-      <c r="G27" s="40" t="s">
+      <c r="F27" s="34"/>
+      <c r="G27" s="85" t="s">
         <v>56</v>
       </c>
-      <c r="H27" s="40"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="40"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="39"/>
+      <c r="H27" s="85"/>
+      <c r="I27" s="85"/>
+      <c r="J27" s="85"/>
+      <c r="K27" s="85"/>
+      <c r="L27" s="34"/>
     </row>
     <row r="28" spans="6:12" x14ac:dyDescent="0.35">
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="39"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
     </row>
     <row r="30" spans="6:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="31" spans="6:12" x14ac:dyDescent="0.35">
@@ -12767,13 +13212,13 @@
       <c r="K34" s="12">
         <v>1792.13</v>
       </c>
-      <c r="M34" s="33"/>
+      <c r="M34" s="29"/>
     </row>
     <row r="35" spans="10:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="J35" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="K35" s="38">
+      <c r="K35" s="33">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
@@ -12800,20 +13245,16 @@
       </c>
     </row>
     <row r="39" spans="10:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J39" s="28" t="s">
+      <c r="J39" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="K39" s="43">
+      <c r="K39" s="36">
         <f>+K34-K37</f>
         <v>2.1999902784775713</v>
       </c>
     </row>
-    <row r="40" spans="10:13" x14ac:dyDescent="0.35">
-      <c r="K40" s="22"/>
-    </row>
     <row r="41" spans="10:13" x14ac:dyDescent="0.35">
-      <c r="J41" s="22"/>
-      <c r="K41" s="42"/>
+      <c r="K41" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12825,7 +13266,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E8E41C0-5F97-462B-BFAB-F264293E8EBD}">
   <dimension ref="B10:E31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -12851,7 +13292,7 @@
       <c r="B12" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12">
         <v>1000</v>
       </c>
       <c r="D12" s="12"/>
@@ -12860,14 +13301,13 @@
       <c r="B13" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="22"/>
       <c r="D13" s="12"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B14" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="54">
+      <c r="C14" s="47">
         <v>0.02</v>
       </c>
       <c r="D14" s="12"/>
@@ -12882,52 +13322,51 @@
       </c>
     </row>
     <row r="19" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="53"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="46"/>
     </row>
     <row r="20" spans="2:5" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B20" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20">
         <f>+C12</f>
         <v>1000</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" t="s">
         <v>70</v>
       </c>
       <c r="E20" s="12"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21" s="11"/>
-      <c r="C21" s="22">
+      <c r="C21">
         <f>+C15</f>
         <v>2500</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" t="s">
         <v>63</v>
       </c>
       <c r="E21" s="12"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" s="11"/>
-      <c r="C22" s="48">
+      <c r="C22" s="41">
         <f>+C20*C21</f>
         <v>2500000</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" t="s">
         <v>64</v>
       </c>
       <c r="E22" s="12"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="11"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22" t="s">
+      <c r="D23" t="s">
         <v>65</v>
       </c>
       <c r="E23" s="12"/>
@@ -12936,41 +13375,40 @@
       <c r="B24" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="49">
+      <c r="C24" s="42">
         <f>+C22</f>
         <v>2500000</v>
       </c>
-      <c r="D24" s="22"/>
       <c r="E24" s="12"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25" s="11"/>
-      <c r="C25" s="48">
+      <c r="C25" s="41">
         <f>+C22*(1+C14)^(C11/12)</f>
         <v>2512407.3289330094</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D25" t="s">
         <v>66</v>
       </c>
       <c r="E25" s="12"/>
     </row>
     <row r="26" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="51" t="s">
+      <c r="B26" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="53"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="46"/>
     </row>
     <row r="27" spans="2:5" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B27" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C27" s="49">
+      <c r="C27" s="42">
         <f>+C25</f>
         <v>2512407.3289330094</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D27" t="s">
         <v>7</v>
       </c>
       <c r="E27" s="12"/>
@@ -12979,11 +13417,11 @@
       <c r="B28" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="49">
+      <c r="C28" s="42">
         <f>+-C27</f>
         <v>-2512407.3289330094</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="D28" t="s">
         <v>69</v>
       </c>
       <c r="E28" s="12"/>
@@ -13003,7 +13441,7 @@
       <c r="B31" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="55">
+      <c r="C31" s="48">
         <f>+C25+C28</f>
         <v>0</v>
       </c>
@@ -13014,7 +13452,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54E00E2B-87A3-426B-B8AF-05C3EA2F03C8}">
   <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13029,18 +13467,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="19" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="86" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="27"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
@@ -13051,7 +13488,9 @@
         <v>970</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="27"/>
+      <c r="F3" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -13063,36 +13502,40 @@
         <v>975</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="27"/>
+      <c r="F4">
+        <v>1000</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="3"/>
+      <c r="B5" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="3">
+        <v>5</v>
+      </c>
       <c r="D5" s="1"/>
-      <c r="E5" s="27"/>
     </row>
     <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
       <c r="B6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="29">
-        <v>0.06</v>
+      <c r="C6" s="25">
+        <v>0.08</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="46" t="s">
+      <c r="F6" s="52"/>
+      <c r="G6" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="60" t="s">
+      <c r="H6" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="61" t="s">
+      <c r="I6" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="60" t="s">
+      <c r="J6" s="53" t="s">
         <v>7</v>
       </c>
     </row>
@@ -13101,63 +13544,60 @@
       <c r="B7" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="30">
-        <v>0.05</v>
+      <c r="C7" s="26">
+        <v>0.02</v>
       </c>
       <c r="D7" s="1"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="60"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="53"/>
     </row>
     <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
       <c r="B8" s="6"/>
       <c r="C8" s="3"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="62" t="s">
+      <c r="G8" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="63">
+      <c r="H8" s="56">
         <f>+$C$9</f>
         <v>1</v>
       </c>
-      <c r="I8" s="64">
+      <c r="I8" s="57">
         <v>0.05</v>
       </c>
-      <c r="J8" s="63"/>
+      <c r="J8" s="56"/>
     </row>
     <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="28">
         <v>1</v>
       </c>
       <c r="D9" s="1"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="50" t="s">
+      <c r="F9" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="62" t="s">
+      <c r="G9" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="63">
+      <c r="H9" s="56">
         <f>+-H8</f>
         <v>-1</v>
       </c>
-      <c r="I9" s="65">
+      <c r="I9" s="58">
         <f>+C3</f>
         <v>970</v>
       </c>
-      <c r="J9" s="63">
+      <c r="J9" s="56">
         <f>+H8*C3</f>
         <v>970</v>
       </c>
@@ -13167,155 +13607,154 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="62" t="s">
+      <c r="G10" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="63"/>
-      <c r="I10" s="64">
+      <c r="H10" s="56"/>
+      <c r="I10" s="57">
         <v>0.08</v>
       </c>
-      <c r="J10" s="63">
+      <c r="J10" s="56">
         <f>-J9</f>
         <v>-970</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="F11" s="50" t="s">
+      <c r="F11" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="G11" s="62" t="s">
+      <c r="G11" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="63"/>
-      <c r="I11" s="65">
+      <c r="H11" s="56"/>
+      <c r="I11" s="58">
         <f>+C4</f>
         <v>975</v>
       </c>
-      <c r="J11" s="63">
+      <c r="J11" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F12" s="66"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="67"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="60"/>
     </row>
     <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F13" s="69"/>
-      <c r="G13" s="70" t="s">
+      <c r="F13" s="62"/>
+      <c r="G13" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="H13" s="71"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="71"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="64"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="F14" s="73" t="s">
+      <c r="F14" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="74" t="s">
+      <c r="G14" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="75"/>
-      <c r="I14" s="76">
+      <c r="H14" s="68"/>
+      <c r="I14" s="69">
         <f>+C6</f>
-        <v>0.06</v>
-      </c>
-      <c r="J14" s="75">
+        <v>0.08</v>
+      </c>
+      <c r="J14" s="68">
         <f>+J9*EXP(1)^I14</f>
-        <v>1029.9814501489989</v>
+        <v>1050.78845564471</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="F15" s="73" t="s">
+      <c r="F15" s="66" t="s">
         <v>76</v>
       </c>
-      <c r="G15" s="77" t="s">
+      <c r="G15" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="78">
+      <c r="H15" s="71">
         <f>+$C$9*EXP(1)^$C$7</f>
-        <v>1.0512710963760241</v>
-      </c>
-      <c r="I15" s="79">
+        <v>1.0202013400267558</v>
+      </c>
+      <c r="I15" s="72">
         <f>+C4</f>
         <v>975</v>
       </c>
-      <c r="J15" s="78">
+      <c r="J15" s="71">
         <f>-H15*I15</f>
-        <v>-1024.9893189666236</v>
+        <v>-994.69630652608691</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F16" s="73" t="s">
+      <c r="F16" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="G16" s="80" t="s">
+      <c r="G16" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="81">
+      <c r="H16" s="74">
         <f>+-H15</f>
-        <v>-1.0512710963760241</v>
-      </c>
-      <c r="I16" s="82">
+        <v>-1.0202013400267558</v>
+      </c>
+      <c r="I16" s="75">
         <f>+C7</f>
-        <v>0.05</v>
-      </c>
-      <c r="J16" s="81"/>
+        <v>0.02</v>
+      </c>
+      <c r="J16" s="74"/>
     </row>
     <row r="17" spans="6:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F17" s="83"/>
-      <c r="G17" s="83"/>
-      <c r="H17" s="84"/>
-      <c r="I17" s="85"/>
-      <c r="J17" s="84"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="78"/>
+      <c r="J17" s="77"/>
     </row>
     <row r="18" spans="6:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F18" s="71"/>
-      <c r="G18" s="83" t="s">
+      <c r="F18" s="64"/>
+      <c r="G18" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="84">
+      <c r="H18" s="77">
         <f>+SUM(H8:H16)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="85"/>
-      <c r="J18" s="86">
+      <c r="I18" s="78"/>
+      <c r="J18" s="79">
         <f>+SUM(J8:J17)</f>
-        <v>4.9921311823752603</v>
-      </c>
-      <c r="K18" s="21">
+        <v>56.09214911862307</v>
+      </c>
+      <c r="K18" s="20">
         <f>+J18*EXP(1)^(-C7)</f>
-        <v>4.7486620716428876</v>
+        <v>54.981450148999023</v>
       </c>
     </row>
     <row r="19" spans="6:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H19" s="56"/>
-      <c r="J19" s="56"/>
+      <c r="H19" s="49"/>
+      <c r="J19" s="49"/>
     </row>
     <row r="20" spans="6:12" x14ac:dyDescent="0.35">
       <c r="G20" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H20" s="44"/>
+      <c r="H20" s="37"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="44">
+      <c r="J20" s="37">
         <f>+I9*(EXP(1)^(C6-C7))</f>
-        <v>979.74866207164291</v>
+        <v>1029.9814501489989</v>
       </c>
     </row>
     <row r="21" spans="6:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G21" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="56"/>
-      <c r="J21" s="56">
+      <c r="H21" s="49"/>
+      <c r="J21" s="49">
         <f>+C4</f>
         <v>975</v>
       </c>
@@ -13324,100 +13763,100 @@
       <c r="G22" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="H22" s="57"/>
+      <c r="H22" s="50"/>
       <c r="I22" s="14"/>
-      <c r="J22" s="57">
+      <c r="J22" s="50">
         <f>+(J20-J21)*C9</f>
-        <v>4.7486620716429115</v>
-      </c>
-      <c r="K22" s="58">
+        <v>54.981450148998874</v>
+      </c>
+      <c r="K22" s="51">
         <f>+J22*EXP(1)^C7</f>
-        <v>4.9921311823752852</v>
+        <v>56.09214911862292</v>
       </c>
     </row>
     <row r="24" spans="6:12" x14ac:dyDescent="0.35">
-      <c r="G24" s="87"/>
-      <c r="H24" s="87"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="87"/>
-      <c r="K24" s="87"/>
-      <c r="L24" s="87"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="80"/>
+      <c r="J24" s="80"/>
+      <c r="K24" s="80"/>
+      <c r="L24" s="80"/>
     </row>
     <row r="25" spans="6:12" x14ac:dyDescent="0.35">
-      <c r="G25" s="87">
+      <c r="G25" s="80">
         <f>+C4</f>
         <v>975</v>
       </c>
-      <c r="H25" s="88" t="str">
+      <c r="H25" s="81" t="str">
         <f>+IF(G25&gt;I25,"&gt;",IF(G25&lt;I25,"&lt;","="))</f>
         <v>&lt;</v>
       </c>
-      <c r="I25" s="87">
+      <c r="I25" s="80">
         <f>+(C3*EXP(1)^C6*EXP(1)^-C7)</f>
-        <v>979.74866207164291</v>
-      </c>
-      <c r="J25" s="88" t="s">
+        <v>1029.9814501489991</v>
+      </c>
+      <c r="J25" s="81" t="s">
         <v>83</v>
       </c>
-      <c r="K25" s="87"/>
-      <c r="L25" s="87"/>
+      <c r="K25" s="80"/>
+      <c r="L25" s="80"/>
     </row>
     <row r="26" spans="6:12" x14ac:dyDescent="0.35">
-      <c r="G26" s="87"/>
-      <c r="H26" s="87"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="87"/>
-      <c r="K26" s="87"/>
-      <c r="L26" s="87"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="80"/>
+      <c r="J26" s="80"/>
+      <c r="K26" s="80"/>
+      <c r="L26" s="80"/>
     </row>
     <row r="27" spans="6:12" x14ac:dyDescent="0.35">
-      <c r="G27" s="88" t="s">
+      <c r="G27" s="81" t="s">
         <v>79</v>
       </c>
-      <c r="H27" s="87"/>
-      <c r="I27" s="87" t="s">
+      <c r="H27" s="80"/>
+      <c r="I27" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="J27" s="87"/>
-      <c r="K27" s="87"/>
-      <c r="L27" s="87"/>
+      <c r="J27" s="80"/>
+      <c r="K27" s="80"/>
+      <c r="L27" s="80"/>
     </row>
     <row r="28" spans="6:12" x14ac:dyDescent="0.35">
-      <c r="G28" s="89">
+      <c r="G28" s="82">
         <f>+(C4-C3)/C3</f>
         <v>5.1546391752577319E-3</v>
       </c>
-      <c r="H28" s="87"/>
-      <c r="I28" s="89">
+      <c r="H28" s="80"/>
+      <c r="I28" s="82">
         <f>+((C3*EXP(1)^C6*EXP(1)^-C7)-C3)/C3</f>
-        <v>1.0050167084167951E-2</v>
-      </c>
-      <c r="J28" s="87" t="s">
+        <v>6.1836546545359895E-2</v>
+      </c>
+      <c r="J28" s="80" t="s">
         <v>81</v>
       </c>
-      <c r="K28" s="87"/>
-      <c r="L28" s="87"/>
+      <c r="K28" s="80"/>
+      <c r="L28" s="80"/>
     </row>
     <row r="29" spans="6:12" x14ac:dyDescent="0.35">
-      <c r="G29" s="87"/>
-      <c r="H29" s="87"/>
-      <c r="I29" s="89">
+      <c r="G29" s="80"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="82">
         <f>+((C3*(1+C6)/(1+C7))-C3)/C3</f>
-        <v>9.5238095238094674E-3</v>
-      </c>
-      <c r="J29" s="87" t="s">
+        <v>5.8823529411764885E-2</v>
+      </c>
+      <c r="J29" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="K29" s="87"/>
-      <c r="L29" s="87"/>
+      <c r="K29" s="80"/>
+      <c r="L29" s="80"/>
     </row>
     <row r="30" spans="6:12" x14ac:dyDescent="0.35">
-      <c r="G30" s="87"/>
-      <c r="H30" s="87"/>
-      <c r="I30" s="87"/>
-      <c r="J30" s="87"/>
-      <c r="K30" s="87"/>
-      <c r="L30" s="87"/>
+      <c r="G30" s="80"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="80"/>
+      <c r="J30" s="80"/>
+      <c r="K30" s="80"/>
+      <c r="L30" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -13426,4 +13865,455 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7492CD26-CFBA-4B4A-AC69-340F8D8D6154}">
+  <dimension ref="C3:P31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="11.6328125" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" customWidth="1"/>
+    <col min="7" max="7" width="3.453125" customWidth="1"/>
+    <col min="9" max="9" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.7265625" customWidth="1"/>
+    <col min="12" max="12" width="16.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:16" ht="16" x14ac:dyDescent="0.4">
+      <c r="D3" s="107" t="s">
+        <v>95</v>
+      </c>
+      <c r="L3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="D5" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="32">
+        <f>1*M5</f>
+        <v>1000</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="G5" s="100"/>
+      <c r="L5" t="s">
+        <v>99</v>
+      </c>
+      <c r="M5">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="D6" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="93">
+        <v>0.1</v>
+      </c>
+      <c r="F6" s="94">
+        <f>+$E$5*E6</f>
+        <v>100</v>
+      </c>
+      <c r="G6" s="101"/>
+      <c r="L6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M6">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="7" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="D7" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="93">
+        <v>0.04</v>
+      </c>
+      <c r="F7" s="32">
+        <f>+E7*E5</f>
+        <v>40</v>
+      </c>
+      <c r="G7" s="100"/>
+    </row>
+    <row r="10" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="I10" s="103"/>
+      <c r="J10" s="104" t="s">
+        <v>111</v>
+      </c>
+      <c r="M10">
+        <v>260</v>
+      </c>
+      <c r="N10" t="s">
+        <v>110</v>
+      </c>
+      <c r="P10">
+        <f>+M10+E13</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="D11" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="G11" s="100"/>
+      <c r="I11" s="105" t="s">
+        <v>5</v>
+      </c>
+      <c r="J11" s="106">
+        <f>+F6</f>
+        <v>100</v>
+      </c>
+      <c r="M11">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D12" s="32">
+        <v>920</v>
+      </c>
+      <c r="E12" s="32">
+        <f>+D12-$M$6</f>
+        <v>-180</v>
+      </c>
+      <c r="F12" s="91">
+        <f>+-D12+$M$6</f>
+        <v>180</v>
+      </c>
+      <c r="G12" s="102"/>
+      <c r="N12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C13" s="92" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="92">
+        <v>940</v>
+      </c>
+      <c r="E13" s="92">
+        <f t="shared" ref="E13:E31" si="0">+D13-$M$6</f>
+        <v>-160</v>
+      </c>
+      <c r="F13" s="92">
+        <f>+-D13+$M$6</f>
+        <v>160</v>
+      </c>
+      <c r="G13" s="102"/>
+      <c r="H13" s="87"/>
+      <c r="I13" s="97" t="s">
+        <v>104</v>
+      </c>
+      <c r="J13" s="98"/>
+      <c r="N13" s="88" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="3:16" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D14" s="32">
+        <v>960</v>
+      </c>
+      <c r="E14" s="32">
+        <f t="shared" si="0"/>
+        <v>-140</v>
+      </c>
+      <c r="F14" s="91">
+        <f t="shared" ref="F14:F31" si="1">+-D14+$M$6</f>
+        <v>140</v>
+      </c>
+      <c r="G14" s="102"/>
+      <c r="H14" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="I14" s="108" t="s">
+        <v>107</v>
+      </c>
+      <c r="J14" s="99" t="s">
+        <v>108</v>
+      </c>
+      <c r="M14" s="89">
+        <f>+F6-I15</f>
+        <v>160</v>
+      </c>
+      <c r="N14" s="90">
+        <f>+I15+M14</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="3:16" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D15" s="32">
+        <v>980</v>
+      </c>
+      <c r="E15" s="32">
+        <f t="shared" si="0"/>
+        <v>-120</v>
+      </c>
+      <c r="F15" s="91">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="G15" s="102"/>
+      <c r="I15" s="95">
+        <f>+J11+E13</f>
+        <v>-60</v>
+      </c>
+      <c r="J15" s="96">
+        <f>+J11+F13</f>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="16" spans="3:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="D16" s="32">
+        <v>1000</v>
+      </c>
+      <c r="E16" s="32">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+      <c r="F16" s="91">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="G16" s="102"/>
+      <c r="L16" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" t="s">
+        <v>109</v>
+      </c>
+      <c r="N16">
+        <f>+J15</f>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="17" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D17" s="32">
+        <v>1020</v>
+      </c>
+      <c r="E17" s="32">
+        <f t="shared" si="0"/>
+        <v>-80</v>
+      </c>
+      <c r="F17" s="91">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="G17" s="102"/>
+    </row>
+    <row r="18" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D18" s="32">
+        <v>1040</v>
+      </c>
+      <c r="E18" s="32">
+        <f t="shared" si="0"/>
+        <v>-60</v>
+      </c>
+      <c r="F18" s="91">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="G18" s="102"/>
+    </row>
+    <row r="19" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D19" s="32">
+        <v>1060</v>
+      </c>
+      <c r="E19" s="32">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="F19" s="91">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="G19" s="102"/>
+      <c r="L19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D20" s="32">
+        <v>1080</v>
+      </c>
+      <c r="E20" s="32">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="F20" s="91">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="G20" s="102"/>
+      <c r="L20" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D21" s="32">
+        <v>1100</v>
+      </c>
+      <c r="E21" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="91">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="102"/>
+    </row>
+    <row r="22" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D22" s="32">
+        <v>1120</v>
+      </c>
+      <c r="E22" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F22" s="91">
+        <f t="shared" si="1"/>
+        <v>-20</v>
+      </c>
+      <c r="G22" s="102"/>
+    </row>
+    <row r="23" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D23" s="32">
+        <v>1140</v>
+      </c>
+      <c r="E23" s="32">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="F23" s="91">
+        <f t="shared" si="1"/>
+        <v>-40</v>
+      </c>
+      <c r="G23" s="102"/>
+    </row>
+    <row r="24" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D24" s="32">
+        <v>1160</v>
+      </c>
+      <c r="E24" s="32">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="F24" s="91">
+        <f t="shared" si="1"/>
+        <v>-60</v>
+      </c>
+      <c r="G24" s="102"/>
+    </row>
+    <row r="25" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D25" s="32">
+        <v>1180</v>
+      </c>
+      <c r="E25" s="32">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="F25" s="91">
+        <f t="shared" si="1"/>
+        <v>-80</v>
+      </c>
+      <c r="G25" s="102"/>
+    </row>
+    <row r="26" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D26" s="32">
+        <v>1200</v>
+      </c>
+      <c r="E26" s="32">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F26" s="91">
+        <f t="shared" si="1"/>
+        <v>-100</v>
+      </c>
+      <c r="G26" s="102"/>
+    </row>
+    <row r="27" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D27" s="32">
+        <v>1220</v>
+      </c>
+      <c r="E27" s="32">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="F27" s="91">
+        <f t="shared" si="1"/>
+        <v>-120</v>
+      </c>
+      <c r="G27" s="102"/>
+    </row>
+    <row r="28" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D28" s="32">
+        <v>1240</v>
+      </c>
+      <c r="E28" s="32">
+        <f t="shared" si="0"/>
+        <v>140</v>
+      </c>
+      <c r="F28" s="91">
+        <f t="shared" si="1"/>
+        <v>-140</v>
+      </c>
+      <c r="G28" s="102"/>
+    </row>
+    <row r="29" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D29" s="32">
+        <v>1260</v>
+      </c>
+      <c r="E29" s="32">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="F29" s="91">
+        <f t="shared" si="1"/>
+        <v>-160</v>
+      </c>
+      <c r="G29" s="102"/>
+    </row>
+    <row r="30" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D30" s="32">
+        <v>1280</v>
+      </c>
+      <c r="E30" s="32">
+        <f t="shared" si="0"/>
+        <v>180</v>
+      </c>
+      <c r="F30" s="91">
+        <f t="shared" si="1"/>
+        <v>-180</v>
+      </c>
+      <c r="G30" s="102"/>
+    </row>
+    <row r="31" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D31" s="32">
+        <v>1300</v>
+      </c>
+      <c r="E31" s="32">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="F31" s="91">
+        <f t="shared" si="1"/>
+        <v>-200</v>
+      </c>
+      <c r="G31" s="102"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>